--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -673,444 +673,518 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>60492</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1080426452</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1589.53</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28389961</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I2" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1290470</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.147759</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2639.06</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.07567699999999999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1351.64</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="S2" t="n">
-        <v>18966.18</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>O:62864 H:62864 L:59175 C:61094</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="n">
+        <v>61094</v>
+      </c>
+      <c r="D2" s="9" t="n">
+        <v>1085640380</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>1627.37</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>28918365</v>
+      </c>
+      <c r="H2" s="16" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>1208005</v>
+      </c>
+      <c r="K2" s="16" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="L2" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M2" s="9" t="n">
+        <v>2617</v>
+      </c>
+      <c r="N2" s="16" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="O2" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P2" s="9" t="n">
+        <v>1346</v>
+      </c>
+      <c r="Q2" s="16" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="R2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>23:45</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>59882</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1069526142</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1579.16</v>
-      </c>
-      <c r="G3" t="n">
-        <v>28204743</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="I3" t="n">
-        <v>71.73</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1281081</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.14444</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2579.79</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-2.98</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.073505</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1312.84</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="S3" t="n">
-        <v>18799.48</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>O:61186 H:61321 L:58189 C:59235</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>59235</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>1052605950</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>1542.96</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>27418399</v>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>68.44</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>1216179</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>2540</v>
+      </c>
+      <c r="N3" s="16" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="O3" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P3" s="9" t="n">
+        <v>1304</v>
+      </c>
+      <c r="Q3" s="16" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="R3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>23:45</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>59713</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1066861806</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1575.71</v>
-      </c>
-      <c r="G4" t="n">
-        <v>28152130</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>73.94</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1320986</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.145283</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2595.69</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.072739</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1299.59</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="S4" t="n">
-        <v>18731.63</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>O:59316 H:60455 L:58801 C:60273</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>60273</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>1071051210</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>1581.48</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>28102900</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I4" s="9" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1274109</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>2609</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>1336</v>
+      </c>
+      <c r="Q4" s="10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>23:45</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>58346</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1046162764</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-2.26</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1563.34</v>
-      </c>
-      <c r="G5" t="n">
-        <v>28031243</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="I5" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1310697</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.143786</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2578.13</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.07058300000000001</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1265.59</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="S5" t="n">
-        <v>18516.15</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>O:60234 H:60784 L:59741 C:60235</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>60235</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1070375950</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1580.6</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>28087262</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>2577</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>1309</v>
+      </c>
+      <c r="Q5" s="16" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="R5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>58357</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1047992098</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1565.64</v>
-      </c>
-      <c r="G6" t="n">
-        <v>28116078</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I6" t="n">
-        <v>74.53</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1338450</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.150403</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2700.98</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.07087</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1272.7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="S6" t="n">
-        <v>18594.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>O:60250 H:60281 L:58935 C:59726</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>59726</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1061331020</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>1568.67</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>27875266</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>72.27</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>1284238</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>2569</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>1292</v>
+      </c>
+      <c r="Q6" s="16" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>60058</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1072868723</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1565.44</v>
-      </c>
-      <c r="G7" t="n">
-        <v>27964729</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I7" t="n">
-        <v>70.42</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1257982</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.14524</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2594.53</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.074227</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1325.97</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.032</v>
-      </c>
-      <c r="S7" t="n">
-        <v>18444.08</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>O:59848 H:60644 L:59023 C:59081</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>59081</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1049869370</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>1575.29</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>27992903</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>73.45999999999999</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>1305384</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>2562</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>1280</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>O:58984 H:59290 L:57945 C:58542</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>58542</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1040291340</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>1567.95</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>27862472</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>1327774</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>2676</v>
+      </c>
+      <c r="N8" s="10" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>1263</v>
+      </c>
+      <c r="Q8" s="16" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
@@ -1127,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1176,161 +1250,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>60492</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Bitcoin Tembus Rp 1,9 M</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>59882</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Bitcoin Tembus Rp 1,9 M</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>59713</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Bitcoin Tembus Rp 1,9 M</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>58346</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-2.26</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bitcoin Tembus Rp 1,9 M</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>58357</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NETRAL</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Bitcoin Tembus Rp 1,9 M</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -686,8 +686,8 @@
       <c r="C2" s="9" t="n">
         <v>61094</v>
       </c>
-      <c r="D2" s="9" t="n">
-        <v>1085640380</v>
+      <c r="D2" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E2" s="16" t="n">
         <v>-2.82</v>
@@ -695,8 +695,8 @@
       <c r="F2" s="9" t="n">
         <v>1627.37</v>
       </c>
-      <c r="G2" s="9" t="n">
-        <v>28918365</v>
+      <c r="G2" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="16" t="n">
         <v>-3.01</v>
@@ -704,8 +704,8 @@
       <c r="I2" s="9" t="n">
         <v>67.98</v>
       </c>
-      <c r="J2" s="9" t="n">
-        <v>1208005</v>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K2" s="16" t="n">
         <v>-2.54</v>
@@ -713,8 +713,8 @@
       <c r="L2" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="M2" s="9" t="n">
-        <v>2617</v>
+      <c r="M2" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N2" s="16" t="n">
         <v>-0.65</v>
@@ -722,20 +722,20 @@
       <c r="O2" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="P2" s="9" t="n">
-        <v>1346</v>
+      <c r="P2" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q2" s="16" t="n">
         <v>-4.07</v>
       </c>
-      <c r="R2" s="8" t="n">
-        <v>0</v>
+      <c r="R2" s="9" t="n">
+        <v>1.07</v>
       </c>
       <c r="S2" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="11" t="n">
-        <v>0</v>
+      <c r="T2" s="16" t="n">
+        <v>-2.37</v>
       </c>
       <c r="U2" s="11" t="n">
         <v>0</v>
@@ -760,8 +760,8 @@
       <c r="C3" s="9" t="n">
         <v>59235</v>
       </c>
-      <c r="D3" s="9" t="n">
-        <v>1052605950</v>
+      <c r="D3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E3" s="16" t="n">
         <v>-3.19</v>
@@ -769,8 +769,8 @@
       <c r="F3" s="9" t="n">
         <v>1542.96</v>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>27418399</v>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H3" s="16" t="n">
         <v>-5.38</v>
@@ -778,8 +778,8 @@
       <c r="I3" s="9" t="n">
         <v>68.44</v>
       </c>
-      <c r="J3" s="9" t="n">
-        <v>1216179</v>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K3" s="10" t="n">
         <v>0.59</v>
@@ -787,8 +787,8 @@
       <c r="L3" s="9" t="n">
         <v>0.14</v>
       </c>
-      <c r="M3" s="9" t="n">
-        <v>2540</v>
+      <c r="M3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N3" s="16" t="n">
         <v>-2.99</v>
@@ -796,20 +796,20 @@
       <c r="O3" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P3" s="9" t="n">
-        <v>1304</v>
+      <c r="P3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q3" s="16" t="n">
         <v>-3.17</v>
       </c>
-      <c r="R3" s="8" t="n">
-        <v>0</v>
+      <c r="R3" s="9" t="n">
+        <v>1.02</v>
       </c>
       <c r="S3" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="11" t="n">
-        <v>0</v>
+      <c r="T3" s="16" t="n">
+        <v>-4.58</v>
       </c>
       <c r="U3" s="11" t="n">
         <v>0</v>
@@ -834,8 +834,8 @@
       <c r="C4" s="9" t="n">
         <v>60273</v>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>1071051210</v>
+      <c r="D4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>1.61</v>
@@ -843,8 +843,8 @@
       <c r="F4" s="9" t="n">
         <v>1581.48</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>28102900</v>
+      <c r="G4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>2.44</v>
@@ -852,8 +852,8 @@
       <c r="I4" s="9" t="n">
         <v>71.7</v>
       </c>
-      <c r="J4" s="9" t="n">
-        <v>1274109</v>
+      <c r="J4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K4" s="10" t="n">
         <v>4.76</v>
@@ -861,8 +861,8 @@
       <c r="L4" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="M4" s="9" t="n">
-        <v>2609</v>
+      <c r="M4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N4" s="10" t="n">
         <v>2.78</v>
@@ -870,20 +870,20 @@
       <c r="O4" s="9" t="n">
         <v>0.08</v>
       </c>
-      <c r="P4" s="9" t="n">
-        <v>1336</v>
+      <c r="P4" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q4" s="10" t="n">
         <v>2.48</v>
       </c>
-      <c r="R4" s="8" t="n">
-        <v>0</v>
+      <c r="R4" s="9" t="n">
+        <v>1.06</v>
       </c>
       <c r="S4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="T4" s="11" t="n">
-        <v>0</v>
+      <c r="T4" s="10" t="n">
+        <v>3.53</v>
       </c>
       <c r="U4" s="11" t="n">
         <v>0</v>
@@ -908,8 +908,8 @@
       <c r="C5" s="9" t="n">
         <v>60235</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>1070375950</v>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="11" t="n">
         <v>0</v>
@@ -917,8 +917,8 @@
       <c r="F5" s="9" t="n">
         <v>1580.6</v>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>28087262</v>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>-0.03</v>
@@ -926,8 +926,8 @@
       <c r="I5" s="9" t="n">
         <v>71.81</v>
       </c>
-      <c r="J5" s="9" t="n">
-        <v>1276064</v>
+      <c r="J5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K5" s="10" t="n">
         <v>0.17</v>
@@ -935,8 +935,8 @@
       <c r="L5" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="M5" s="9" t="n">
-        <v>2577</v>
+      <c r="M5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N5" s="16" t="n">
         <v>-1.32</v>
@@ -944,20 +944,20 @@
       <c r="O5" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P5" s="9" t="n">
-        <v>1309</v>
+      <c r="P5" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q5" s="16" t="n">
         <v>-2.02</v>
       </c>
-      <c r="R5" s="8" t="n">
-        <v>0</v>
+      <c r="R5" s="9" t="n">
+        <v>1.05</v>
       </c>
       <c r="S5" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="11" t="n">
-        <v>0</v>
+      <c r="T5" s="16" t="n">
+        <v>-0.66</v>
       </c>
       <c r="U5" s="11" t="n">
         <v>0</v>
@@ -982,8 +982,8 @@
       <c r="C6" s="9" t="n">
         <v>59726</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>1061331020</v>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>-0.87</v>
@@ -991,8 +991,8 @@
       <c r="F6" s="9" t="n">
         <v>1568.67</v>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>27875266</v>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H6" s="16" t="n">
         <v>-0.71</v>
@@ -1000,8 +1000,8 @@
       <c r="I6" s="9" t="n">
         <v>72.27</v>
       </c>
-      <c r="J6" s="9" t="n">
-        <v>1284238</v>
+      <c r="J6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K6" s="10" t="n">
         <v>0.61</v>
@@ -1009,8 +1009,8 @@
       <c r="L6" s="9" t="n">
         <v>0.14</v>
       </c>
-      <c r="M6" s="9" t="n">
-        <v>2569</v>
+      <c r="M6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N6" s="16" t="n">
         <v>-0.45</v>
@@ -1018,20 +1018,20 @@
       <c r="O6" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P6" s="9" t="n">
-        <v>1292</v>
+      <c r="P6" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q6" s="16" t="n">
         <v>-1.42</v>
       </c>
-      <c r="R6" s="8" t="n">
-        <v>0</v>
+      <c r="R6" s="9" t="n">
+        <v>1.05</v>
       </c>
       <c r="S6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="11" t="n">
-        <v>0</v>
+      <c r="T6" s="16" t="n">
+        <v>-0.1</v>
       </c>
       <c r="U6" s="11" t="n">
         <v>0</v>
@@ -1056,8 +1056,8 @@
       <c r="C7" s="9" t="n">
         <v>59081</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>1049869370</v>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>-1.28</v>
@@ -1065,8 +1065,8 @@
       <c r="F7" s="9" t="n">
         <v>1575.29</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>27992903</v>
+      <c r="G7" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.24</v>
@@ -1074,8 +1074,8 @@
       <c r="I7" s="9" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="J7" s="9" t="n">
-        <v>1305384</v>
+      <c r="J7" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K7" s="10" t="n">
         <v>1.58</v>
@@ -1083,8 +1083,8 @@
       <c r="L7" s="9" t="n">
         <v>0.14</v>
       </c>
-      <c r="M7" s="9" t="n">
-        <v>2562</v>
+      <c r="M7" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N7" s="16" t="n">
         <v>-0.31</v>
@@ -1092,20 +1092,20 @@
       <c r="O7" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P7" s="9" t="n">
-        <v>1280</v>
+      <c r="P7" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" s="16" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="R7" s="8" t="n">
-        <v>0</v>
+      <c r="R7" s="9" t="n">
+        <v>1.04</v>
       </c>
       <c r="S7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="11" t="n">
-        <v>0</v>
+      <c r="T7" s="16" t="n">
+        <v>-1.33</v>
       </c>
       <c r="U7" s="11" t="n">
         <v>0</v>
@@ -1130,8 +1130,8 @@
       <c r="C8" s="9" t="n">
         <v>58542</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <v>1040291340</v>
+      <c r="D8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>-0.75</v>
@@ -1139,8 +1139,8 @@
       <c r="F8" s="9" t="n">
         <v>1567.95</v>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>27862472</v>
+      <c r="G8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="16" t="n">
         <v>-0.35</v>
@@ -1148,8 +1148,8 @@
       <c r="I8" s="9" t="n">
         <v>74.72</v>
       </c>
-      <c r="J8" s="9" t="n">
-        <v>1327774</v>
+      <c r="J8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K8" s="10" t="n">
         <v>1.95</v>
@@ -1157,8 +1157,8 @@
       <c r="L8" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="M8" s="9" t="n">
-        <v>2676</v>
+      <c r="M8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N8" s="10" t="n">
         <v>4.73</v>
@@ -1166,14 +1166,14 @@
       <c r="O8" s="9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P8" s="9" t="n">
-        <v>1263</v>
+      <c r="P8" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="Q8" s="16" t="n">
         <v>-0.42</v>
       </c>
-      <c r="R8" s="8" t="n">
-        <v>0</v>
+      <c r="R8" s="9" t="n">
+        <v>1.04</v>
       </c>
       <c r="S8" s="8" t="n">
         <v>0</v>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sentimen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sentimen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1190,6 +1190,154 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>O:58467 H:60359 L:58279 C:60091</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>60091</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1618.73</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>77.15000000000001</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O9" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="R9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>O:61225 H:62060 L:61140 C:61552</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>61552</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>1696</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>80.59</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sentimen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sentimen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -673,666 +673,740 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>O:62864 H:62864 L:59175 C:61094</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n">
+      <c r="C2" t="n">
         <v>61094</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>-2.82</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" t="n">
         <v>1627.37</v>
       </c>
-      <c r="G2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="16" t="n">
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>-3.01</v>
       </c>
-      <c r="I2" s="9" t="n">
+      <c r="I2" t="n">
         <v>67.98</v>
       </c>
-      <c r="J2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="16" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>-2.54</v>
       </c>
-      <c r="L2" s="9" t="n">
+      <c r="L2" t="n">
         <v>0.15</v>
       </c>
-      <c r="M2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" s="16" t="n">
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>-0.65</v>
       </c>
-      <c r="O2" s="9" t="n">
+      <c r="O2" t="n">
         <v>0.08</v>
       </c>
-      <c r="P2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="16" t="n">
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-4.07</v>
       </c>
-      <c r="R2" s="9" t="n">
+      <c r="R2" t="n">
         <v>1.07</v>
       </c>
-      <c r="S2" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" s="16" t="n">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>-2.37</v>
       </c>
-      <c r="U2" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>O:61186 H:61321 L:58189 C:59235</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n">
+      <c r="C3" t="n">
         <v>59235</v>
       </c>
-      <c r="D3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>-3.19</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" t="n">
         <v>1542.96</v>
       </c>
-      <c r="G3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16" t="n">
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>-5.38</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" t="n">
         <v>68.44</v>
       </c>
-      <c r="J3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="10" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.59</v>
       </c>
-      <c r="L3" s="9" t="n">
+      <c r="L3" t="n">
         <v>0.14</v>
       </c>
-      <c r="M3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="16" t="n">
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>-2.99</v>
       </c>
-      <c r="O3" s="9" t="n">
+      <c r="O3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="16" t="n">
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-3.17</v>
       </c>
-      <c r="R3" s="9" t="n">
+      <c r="R3" t="n">
         <v>1.02</v>
       </c>
-      <c r="S3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="16" t="n">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>-4.58</v>
       </c>
-      <c r="U3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>O:59316 H:60455 L:58801 C:60273</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" t="n">
         <v>60273</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10" t="n">
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>1.61</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" t="n">
         <v>1581.48</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10" t="n">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.44</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" t="n">
         <v>71.7</v>
       </c>
-      <c r="J4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="10" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.76</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" t="n">
         <v>0.15</v>
       </c>
-      <c r="M4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="10" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.78</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" t="n">
         <v>0.08</v>
       </c>
-      <c r="P4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="10" t="n">
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2.48</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" t="n">
         <v>1.06</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="10" t="n">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.53</v>
       </c>
-      <c r="U4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>O:60234 H:60784 L:59741 C:60235</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" t="n">
         <v>60235</v>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>1580.6</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="16" t="n">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>-0.03</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" t="n">
         <v>71.81</v>
       </c>
-      <c r="J5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="10" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>0.17</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" t="n">
         <v>0.15</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="16" t="n">
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>-1.32</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="16" t="n">
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-2.02</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" t="n">
         <v>1.05</v>
       </c>
-      <c r="S5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="16" t="n">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>-0.66</v>
       </c>
-      <c r="U5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>O:60250 H:60281 L:58935 C:59726</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" t="n">
         <v>59726</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>-0.87</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" t="n">
         <v>1568.67</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="16" t="n">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>-0.71</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" t="n">
         <v>72.27</v>
       </c>
-      <c r="J6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="10" t="n">
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.61</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" t="n">
         <v>0.14</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="16" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>-0.45</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="16" t="n">
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.42</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" t="n">
         <v>1.05</v>
       </c>
-      <c r="S6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="16" t="n">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>-0.1</v>
       </c>
-      <c r="U6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>O:59848 H:60644 L:59023 C:59081</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" t="n">
         <v>59081</v>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>-1.28</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" t="n">
         <v>1575.29</v>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10" t="n">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.24</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" t="n">
         <v>73.45999999999999</v>
       </c>
-      <c r="J7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="10" t="n">
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1.58</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" t="n">
         <v>0.14</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="16" t="n">
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>-0.31</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="16" t="n">
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" t="n">
         <v>1.04</v>
       </c>
-      <c r="S7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="16" t="n">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>-1.33</v>
       </c>
-      <c r="U7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>O:58984 H:59290 L:57945 C:58542</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" t="n">
         <v>58542</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>-0.75</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" t="n">
         <v>1567.95</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="16" t="n">
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>-0.35</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" t="n">
         <v>74.72</v>
       </c>
-      <c r="J8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1.95</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" t="n">
         <v>0.15</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>4.73</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="16" t="n">
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.42</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" t="n">
         <v>1.04</v>
       </c>
-      <c r="S8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>O:58467 H:60359 L:58279 C:60091</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" t="n">
         <v>60091</v>
       </c>
-      <c r="D9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10" t="n">
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>2.78</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" t="n">
         <v>1618.73</v>
       </c>
-      <c r="G9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="n">
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>3.31</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" t="n">
         <v>77.15000000000001</v>
       </c>
-      <c r="J9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="10" t="n">
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.27</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" t="n">
         <v>0.16</v>
       </c>
-      <c r="M9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="10" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.15</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="O9" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="10" t="n">
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3.17</v>
       </c>
-      <c r="R9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>O:61225 H:62060 L:61140 C:61552</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" t="n">
         <v>61552</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="10" t="n">
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>0.53</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" t="n">
         <v>1696</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="10" t="n">
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.03</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" t="n">
         <v>80.59</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="16" t="n">
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>-1.96</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" t="n">
         <v>0.16</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="10" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.87</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="10" t="n">
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.54</v>
       </c>
-      <c r="R10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>O:62064 H:62284 L:61734 C:62180</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>62180</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1744.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1412,6 +1412,80 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>O:0 H:0 L:0 C:0</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1778.96</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>81.63</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1486,6 +1486,154 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>O:62615 H:63857 L:62530 C:63546</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>63546</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1783.45</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I13" t="n">
+        <v>80.93000000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>O:61945 H:63879 L:61339 C:63712</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>63712</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>1799.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1635,74 +1635,148 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>O:62246 H:62313 L:61550 C:62196</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" t="n">
         <v>62196</v>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>-0.08</v>
       </c>
-      <c r="F15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="9" t="n">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="10" t="n">
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0.6</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" t="n">
         <v>1.09</v>
       </c>
-      <c r="S15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="10" t="n">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>0.28</v>
       </c>
-      <c r="U15" s="11" t="n">
+      <c r="U15" t="n">
         <v>1.59</v>
       </c>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>O:62727 H:63075 L:62506 C:62819</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>62819</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1134518930</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1738.38</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>31395358</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>77.62</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1401827</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>3070</v>
+      </c>
+      <c r="N16" s="16" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>1264</v>
+      </c>
+      <c r="Q16" s="10" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S16" s="9" t="n">
+        <v>19686</v>
+      </c>
+      <c r="T16" s="16" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="U16" s="11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sentimen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Harga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sentimen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1709,74 +1709,296 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>O:62727 H:63075 L:62506 C:62819</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" t="n">
         <v>62819</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" t="n">
         <v>1134518930</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" t="n">
         <v>0.15</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" t="n">
         <v>1738.38</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" t="n">
         <v>31395358</v>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" t="n">
         <v>-0.16</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" t="n">
         <v>77.62</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" t="n">
         <v>1401827</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" t="n">
         <v>0.1</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" t="n">
         <v>0.17</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" t="n">
         <v>3070</v>
       </c>
-      <c r="N16" s="16" t="n">
+      <c r="N16" t="n">
         <v>-1.82</v>
       </c>
-      <c r="O16" s="9" t="n">
+      <c r="O16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="P16" s="9" t="n">
+      <c r="P16" t="n">
         <v>1264</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="Q16" t="n">
         <v>0.24</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" t="n">
         <v>1.09</v>
       </c>
-      <c r="S16" s="9" t="n">
+      <c r="S16" t="n">
         <v>19686</v>
       </c>
-      <c r="T16" s="16" t="n">
+      <c r="T16" t="n">
         <v>-0.18</v>
       </c>
-      <c r="U16" s="11" t="n">
+      <c r="U16" t="n">
         <v>1.61</v>
       </c>
-      <c r="V16" s="8" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>O:64360 H:64554 L:64122 C:64256</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>64256</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1160671889</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1793.51</v>
+      </c>
+      <c r="G17" t="n">
+        <v>32396611</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="I17" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1410378</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>O:64142 H:64419 L:63975 C:64110</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>64110</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1159144130</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1813.12</v>
+      </c>
+      <c r="G18" t="n">
+        <v>32782209</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I18" t="n">
+        <v>78.13</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1412633</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>O:63941 H:64172 L:63938 C:64124</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>64124</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>1159396934</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>1820.05</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>32907498</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>77.41</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>1399615</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1931,74 +1931,222 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>O:63941 H:64172 L:63938 C:64124</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" t="n">
         <v>64124</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" t="n">
         <v>1159396934</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" t="n">
         <v>0.29</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" t="n">
         <v>1820.05</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" t="n">
         <v>32907498</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="H19" t="n">
         <v>0.99</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" t="n">
         <v>77.41</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" t="n">
         <v>1399615</v>
       </c>
-      <c r="K19" s="10" t="n">
+      <c r="K19" t="n">
         <v>0.58</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="11" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.55</v>
       </c>
-      <c r="V19" s="8" t="inlineStr">
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>O:62843 H:62843 L:62183 C:62549</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>62549</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1130911941</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1775.33</v>
+      </c>
+      <c r="G20" t="n">
+        <v>32098705</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="I20" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1369772</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>O:62782 H:64783 L:62728 C:64668</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>64668</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>1167127352</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1873.84</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>33819044</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>1397456</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>

--- a/data/crypto_monitor.xlsx
+++ b/data/crypto_monitor.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2079,74 +2079,666 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>O:62782 H:64783 L:62728 C:64668</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" t="n">
         <v>64668</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" t="n">
         <v>1167127352</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" t="n">
         <v>1873.84</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" t="n">
         <v>33819044</v>
       </c>
-      <c r="H21" s="10" t="n">
+      <c r="H21" t="n">
         <v>4.32</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" t="n">
         <v>77.43000000000001</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" t="n">
         <v>1397456</v>
       </c>
-      <c r="K21" s="10" t="n">
+      <c r="K21" t="n">
         <v>2.79</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="11" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.57</v>
       </c>
-      <c r="V21" s="8" t="inlineStr">
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>O:64675 H:65437 L:64592 C:65364</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>65364</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1179946107</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1930.02</v>
+      </c>
+      <c r="G22" t="n">
+        <v>34840579</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I22" t="n">
+        <v>78.06999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1409314</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>O:64194 H:64753 L:63866 C:64706</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>64706</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1162426270</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1881.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33800653</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="I23" t="n">
+        <v>76.66</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1377177</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2874</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>O:63254 H:63346 L:62528 C:63343</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>63343</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1136304162</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1823.96</v>
+      </c>
+      <c r="G24" t="n">
+        <v>32719848</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="I24" t="n">
+        <v>74.48</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1336090</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2870</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>O:64079 H:64181 L:63938 C:64076</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>64076</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1149678820</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1843.03</v>
+      </c>
+      <c r="G25" t="n">
+        <v>33068427</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I25" t="n">
+        <v>74.92</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1344246</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2871</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>O:64394 H:64542 L:64275 C:64522</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>64522</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1157673835</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1869.57</v>
+      </c>
+      <c r="G26" t="n">
+        <v>33544408</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1367204</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3050</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>O:64727 H:65501 L:64176 C:65501</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>65501</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1173321914</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1899.72</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34029757</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1389694</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3045</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>O:66276 H:66840 L:66225 C:66664</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>66664</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1194729623</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1930.64</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34600276</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I28" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1398248</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3047</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>NETRAL ⚪</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>O:65967 H:66056 L:65537 C:65973</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>65973</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1181008267</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>1940.95</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>34745699</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>78.42</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>1403827</v>
+      </c>
+      <c r="K29" s="10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>3222</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="O29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t>NETRAL ⚪</t>
         </is>
